--- a/bills/JXZFSP01/-5196988197/580e25957a3fc4ae3099113b5831765740ede75fe8ce3e4f58f31725ec8698ce/bill-2026-10-22.xlsx
+++ b/bills/JXZFSP01/-5196988197/580e25957a3fc4ae3099113b5831765740ede75fe8ce3e4f58f31725ec8698ce/bill-2026-10-22.xlsx
@@ -157,45 +157,30 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10/22 00:15:55</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4547</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -207,7 +192,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -219,24 +204,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4547</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>-4547</t>
+          <t>0</t>
         </is>
       </c>
     </row>
